--- a/client_data/client_002/leads.xlsx
+++ b/client_data/client_002/leads.xlsx
@@ -38,7 +38,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -57,12 +57,6 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -76,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -85,9 +79,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -531,29 +522,29 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>cafes in Pune</t>
+          <t>restaurants in Pune</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Cafe Goodluck</t>
+          <t>Blue Nile</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Ferguson College Rd, near Goodluck Chowk, Deccan Gymkhana, Pune, Maharashtra 411004, India</t>
+          <t>102, Bund Garden Rd, Agarkar Nagar, Pune, Maharashtra 411001, India</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>099233 64756</t>
+          <t>020 2612 5238</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>52046</v>
+        <v>18325</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -572,29 +563,29 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>cafes in Pune</t>
+          <t>restaurants in Nashik</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>German Bakery</t>
+          <t>Curry Leaves Pure Veg , Jehan Circle</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>292, N Main Rd, Ragvilas Society, Koregaon Park, Pune, Maharashtra 411001, India</t>
+          <t>Jehan Circle, Gangapur Road, Ram Nagar, Ashtavinayak Colony, Veer Sawarkar Nagar, Nashik, Maharashtra 422013, India</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>072760 70390</t>
+          <t>077220 15994</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>14484</v>
+        <v>11467</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -613,29 +604,29 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>restaurants in Pune</t>
+          <t>restaurants in Nashik</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Le Plaisir</t>
+          <t>Veg Aroma</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Rajkamal Survey No. 759/125, Prabhat Road, Opposite Cox and Kings, Near, Kelkar Nursing Home, Deccan Gymkhana, Pune, Maharashtra 411004, India</t>
+          <t>2P6W+P88, Gangapur Rd, Navshya Ganapati Parisar, Kale Nagar, Ganpati Nagar, Anandvalli, Nashik, Maharashtra 422013, India</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>085509 95835</t>
+          <t>083800 32373</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>11785</v>
+        <v>7312</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -654,29 +645,29 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>restaurants in Pune</t>
+          <t>restaurants in Nashik</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Elephant and Co. Kalyani Nagar</t>
+          <t>Bon Vivant</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Metro Traders Compound Complex, Pushpak Society, Plot no. 88, Kalyani Nagar, Pune, Maharashtra 411006, India</t>
+          <t>Patil Park, opposite to Dongre Vasti Gruha, Old Gangapur Naka, Patil Colony, Nashik, Maharashtra 422005, India</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>097668 38529</t>
+          <t>0253 231 4460</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>7977</v>
+        <v>7112</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -695,29 +686,29 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>restaurants in Pune</t>
+          <t>restaurants in Nashik</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>11 East Street Cafe</t>
+          <t>River Dine Restaurant &amp; Banquet</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Virvani Plaza, 11, East St, Camp, Pune, Maharashtra 411001, India</t>
+          <t>Aashram Bridge, Opp, Asaram Bapu Bridge, near Nandawan Lawns, off Gangapur Road, Abhiyanta Naksh Colony, Extension, Savarkar Nagar, Nashik, Maharashtra 422013, India</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>099606 17811</t>
+          <t>099232 73444</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>4125</v>
+        <v>3143</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -736,29 +727,29 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>cafes in Pune</t>
+          <t>restaurants in Nashik</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Coffee Nation - Law College Road</t>
+          <t>The Cobble Street (TCS)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Ashok Path, Shanti Sheela Society, Apex Colony, Erandwane, Pune, Maharashtra 411038, India</t>
+          <t>Gangapur-Savargaon Rd, Nashik, Maharashtra 422012, India</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>083089 81700</t>
+          <t>083809 98099</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>2891</v>
+        <v>2799</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -777,29 +768,29 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>restaurants in Pune</t>
+          <t>restaurants in Nashik</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Thyme &amp; Whisk</t>
+          <t>Udupi Tadka High Gardens Pure Veg restaurant</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Unit B1 &amp; LG01, Jewel Square mall, next to Bharat Petroleum, Vasani Nagar, Koregaon Park, Pune, Maharashtra 411001, India</t>
+          <t>Ashoka Marg, Siddhivinayak Park, Kalpataru Nagar, Nashik, Maharashtra 422011, India</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>088505 45057</t>
+          <t>089560 36925</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1940</v>
+        <v>2397</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
@@ -818,29 +809,29 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>cafes in Pune</t>
+          <t>restaurants in Nashik</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>One O Eight Lifestyle Cafe</t>
+          <t>The Namastey Nashik – Best Pure Veg Restaurant</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Pingale Farms, S Main Rd, behind Blossom Boulevard, Ashok Chakra Society, Iricen Railway Colony, Koregaon Park, Pune, Maharashtra 411001, India</t>
+          <t>Shop No.1, Ganesh gunjan apartment, Lawate nagar, Lavate Nager, Parijat Nagar, Nashik, Maharashtra 422002, India</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>070710 81080</t>
+          <t>0253 299 5031</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1688</v>
+        <v>2179</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -859,29 +850,29 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>restaurants in Pune</t>
+          <t>cafes in Nashik</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>High Garden</t>
+          <t>mykonos - Nashik</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>8th Floor, Next Gen Avenue, Senapati Bapat Rd, near Icc Trade Tower, Bahiratwadi, Bhageerath, Shivajinagar, Pune, Maharashtra 411016, India</t>
+          <t>Plot no. 37, 38, College Rd, Yeolekar Mala, Krishi Nagar, Nashik, Maharashtra 422005, India</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>075582 02453</t>
+          <t>093597 95401</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1430</v>
+        <v>1622</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
@@ -900,29 +891,29 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>cafes in Pune</t>
+          <t>cafes in Nashik</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Cafe - The Voyage</t>
+          <t>Oliv- Taste the Calm</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>A-2, Cafe - The Voyage, Ground Floor Ashiyana Park, Koregaon Park, North main road, lane, 5, Liberty Phase 2, Ragvilas Society, Koregaon Park, Pune, Maharashtra 411001, India</t>
+          <t>College Rd, behind HDFC bank, Thatte Nagar, Nashik, Maharashtra 422005, India</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>085969 50267</t>
+          <t>082755 82899</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1307</v>
+        <v>972</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -941,29 +932,29 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>restaurants in Pune</t>
+          <t>restaurants in Nashik</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>TSUKI : Asian Restaurant</t>
+          <t>Flying Monk</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7, A Lane, Ashok Chakra Society, Vasani Nagar, Koregaon Park, Pune, Maharashtra 411001, India</t>
+          <t>3rd floor, College Rd, behind Big Bazaar, Ramdas Colony, Nashik, Maharashtra 422005, India</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>091721 14339</t>
+          <t>095617 05405</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1107</v>
+        <v>880</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
@@ -982,29 +973,29 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>cafes in Pune</t>
+          <t>cafes in Nashik</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Bookavibe - Book Cafe and Co-working space</t>
+          <t>Cafe Cluster</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Book A Vibe, Ground Floor, Rachana Tulips, Ferguson College Rd, behind Times of India, near Vaishali Hotel, Ganeshwadi, Shivajinagar, Pune, Maharashtra 411004, India</t>
+          <t>02, Disha Apartment, Besides, Wines, Gangapur Rd, D'souza Colony, Nashik, Maharashtra 422005, India</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>070300 73737</t>
+          <t>079722 32147</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>859</v>
+        <v>848</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
@@ -1028,24 +1019,24 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CAFE MHUZO GOA</t>
+          <t>6 story | Qahani</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1229, Ferguson College Rd, Shivajinagar, Pune, Maharashtra 411004, India</t>
+          <t>Sr. No - 13, A/1/2/3, Mullick Nagar, Wadgaon Sheri, Pune, Maharashtra 411014, India</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>095118 98593</t>
+          <t>092846 85990</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>826</v>
+        <v>693</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
@@ -1064,45 +1055,41 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>cafes in Pune</t>
+          <t>cafes in Nashik</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Vohuman Cafe</t>
+          <t>The Breakfast Story Cafe &amp; Bistro</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Millenium Star, Chatrapati Shahu Maharaj Rd, near Ruby Hall, Sangamvadi, Pune, Maharashtra 411001, India</t>
+          <t>Girikale Complex, College Rd, opp. KFC, Thatte Nagar, Nashik, Maharashtra 422005, India</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>093733 23263</t>
+          <t>097673 63709</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>15277</v>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>Social media only</t>
+        <v>509</v>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>No website</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Good social presence, missing a proper website</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>https://m.facebook.com/vohumancafe/</t>
-        </is>
-      </c>
+          <t>Strong reviews, no way to showcase/book online</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
     </row>
@@ -1114,40 +1101,36 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Chafa Cafe And Studio</t>
+          <t>Matcha Brew &amp; Bake</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>A1, Aadit Enclave Building, Lane Number 5, S Main Rd, Suyojana Society, Kavadewadi, Koregaon Park, Pune, Maharashtra 411001, India</t>
+          <t>Survey No.21, A/10, B Plot, S Main Rd, Ashok Chakra Society, Meera Nagar, Koregaon Park, Pune, Maharashtra 411001, India</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>097671 00022</t>
+          <t>099993 09921</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>2252</v>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>Social media only</t>
+        <v>214</v>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>No website</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Good social presence, missing a proper website</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/chafacafeandstudio/</t>
-        </is>
-      </c>
+          <t>Strong reviews, no way to showcase/book online</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
     </row>

--- a/client_data/client_002/leads.xlsx
+++ b/client_data/client_002/leads.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Leads" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$K$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$L$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,7 +38,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -57,6 +57,12 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -70,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -79,6 +85,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -446,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -460,6 +469,7 @@
     <col width="32" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -510,10 +520,15 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>E-commerce Platform</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Weak Points</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>PageSpeed Score (mobile)</t>
         </is>
@@ -522,29 +537,29 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>restaurants in Pune</t>
+          <t>cafes in Pune</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Blue Nile</t>
+          <t>CAFE PETER, Viman Nagar</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>102, Bund Garden Rd, Agarkar Nagar, Pune, Maharashtra 411001, India</t>
+          <t>Anand Square, Opposite Symbosis International College, New Airport Rd, Sakore Nagar, Viman Nagar, Pune, Maharashtra 411014, India</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>020 2612 5238</t>
+          <t>070309 86211</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>18325</v>
+        <v>5422</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -559,33 +574,34 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>restaurants in Nashik</t>
+          <t>cafes in Pune</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Curry Leaves Pure Veg , Jehan Circle</t>
+          <t>The French Window Patisserie</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Jehan Circle, Gangapur Road, Ram Nagar, Ashtavinayak Colony, Veer Sawarkar Nagar, Nashik, Maharashtra 422013, India</t>
+          <t>Lane Number 5, next to Malaka Spice, Ganga Fortune Society, Meera Nagar, Koregaon Park, Pune, Maharashtra 411001, India</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>077220 15994</t>
+          <t>097666 44202</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
         <v>4.3</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>11467</v>
+        <v>1765</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -600,33 +616,34 @@
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>restaurants in Nashik</t>
+          <t>cafes in Pune</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Veg Aroma</t>
+          <t>Butter Brews</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2P6W+P88, Gangapur Rd, Navshya Ganapati Parisar, Kale Nagar, Ganpati Nagar, Anandvalli, Nashik, Maharashtra 422013, India</t>
+          <t>14, Sanas Corner, Lane Number 5, Suyojana Society, Kavadewadi, Koregaon Park, Pune, Maharashtra 411001, India</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>083800 32373</t>
+          <t>088477 17301</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>7312</v>
+        <v>1014</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -641,33 +658,34 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>restaurants in Nashik</t>
+          <t>cafes in Nashik</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Bon Vivant</t>
+          <t>Coffee Club NX</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Patil Park, opposite to Dongre Vasti Gruha, Old Gangapur Naka, Patil Colony, Nashik, Maharashtra 422005, India</t>
+          <t>Pranav Apartment, Shop No-3&amp;4 Besides Facelook Salon, Patil Lane, 4, College Rd, Patil Colony, Nashik, Maharashtra 422005, India</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0253 231 4460</t>
+          <t>094212 90675</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>7112</v>
+        <v>931</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -682,33 +700,34 @@
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>restaurants in Nashik</t>
+          <t>cafes in Nashik</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>River Dine Restaurant &amp; Banquet</t>
+          <t>Pokket cafe College Road</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Aashram Bridge, Opp, Asaram Bapu Bridge, near Nandawan Lawns, off Gangapur Road, Abhiyanta Naksh Colony, Extension, Savarkar Nagar, Nashik, Maharashtra 422013, India</t>
+          <t>Shop No G29-30, S.K Open Mall, College Rd, Ramdas Colony, Nashik, Maharashtra 422005, India</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>099232 73444</t>
+          <t>085303 68669</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>3143</v>
+        <v>630</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -723,33 +742,34 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>restaurants in Nashik</t>
+          <t>cafes in Pune</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>The Cobble Street (TCS)</t>
+          <t>Midori Coffee and Eatery</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Gangapur-Savargaon Rd, Nashik, Maharashtra 422012, India</t>
+          <t>ground floor, Sai Raj Apartments, behind Limelight Studio, Baner, Pune, Maharashtra 411045, India</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>083809 98099</t>
+          <t>080107 52845</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>2799</v>
+        <v>565</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -764,33 +784,34 @@
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>restaurants in Nashik</t>
+          <t>cafes in Pune</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Udupi Tadka High Gardens Pure Veg restaurant</t>
+          <t>The Western Cafe</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Ashoka Marg, Siddhivinayak Park, Kalpataru Nagar, Nashik, Maharashtra 422011, India</t>
+          <t>703, Taboot St, opp. Husseny Bakery, Camp, Pune, Maharashtra 411001, India</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>089560 36925</t>
+          <t>093073 50902</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>2397</v>
+        <v>379</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
@@ -805,33 +826,34 @@
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>restaurants in Nashik</t>
+          <t>cafes in Nashik</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>The Namastey Nashik – Best Pure Veg Restaurant</t>
+          <t>The Leaf</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Shop No.1, Ganesh gunjan apartment, Lawate nagar, Lavate Nager, Parijat Nagar, Nashik, Maharashtra 422002, India</t>
+          <t>Basement 1, Anandrupa, Dr BS Moonje Marg, below John Players, Wellness Forever Side to Sachi Honda, Samartha Nagar, Mahatma Nagar, Parijat Nagar, Nashik, Maharashtra 422005, India</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0253 299 5031</t>
+          <t>097671 11027</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>2179</v>
+        <v>196</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -846,6 +868,7 @@
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -855,24 +878,24 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>mykonos - Nashik</t>
+          <t>Cafe Sanjeevani</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Plot no. 37, 38, College Rd, Yeolekar Mala, Krishi Nagar, Nashik, Maharashtra 422005, India</t>
+          <t>Shop no 12, Sai ratan complex B, Motwani Rd, opposite to utsav Mangal hall, Nashik Road, Nashik, Maharashtra 422101, India</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>093597 95401</t>
+          <t>098607 25155</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1622</v>
+        <v>179</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
@@ -887,6 +910,7 @@
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -896,79 +920,85 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Oliv- Taste the Calm</t>
+          <t>D’mora cafe &amp; Bistro</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>College Rd, behind HDFC bank, Thatte Nagar, Nashik, Maharashtra 422005, India</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>082755 82899</t>
-        </is>
-      </c>
+          <t>4, Patil Lane Number 4, Patil Colony, Canada Corner, Nashik, Maharashtra 422005, India</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>972</v>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>No website</t>
+        <v>420</v>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Social media only</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Strong reviews, no way to showcase/book online</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr"/>
+          <t>Good social presence, missing a proper website</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/dmora_cafe?igshid=YmMyMTA2M2Y=</t>
+        </is>
+      </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>restaurants in Nashik</t>
+          <t>cafes in Pune</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Flying Monk</t>
+          <t>Cafe From The Tree, KP</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3rd floor, College Rd, behind Big Bazaar, Ramdas Colony, Nashik, Maharashtra 422005, India</t>
+          <t>Flat no 2, Zeenat Cooperative Society, A Ln, Vaswani Nagar, Ragvilas Society, Koregaon Park, Pune, Maharashtra 411001, India</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>095617 05405</t>
+          <t>080104 70334</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>880</v>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>No website</t>
+        <v>387</v>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Social media only</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Strong reviews, no way to showcase/book online</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr"/>
+          <t>Good social presence, missing a proper website</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cafefromthetree/</t>
+        </is>
+      </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -978,164 +1008,46 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Cafe Cluster</t>
+          <t>Purohit's cafe</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>02, Disha Apartment, Besides, Wines, Gangapur Rd, D'souza Colony, Nashik, Maharashtra 422005, India</t>
+          <t>College Rd, behind Zudio, Yeolekar Mala, Ramdas Colony, Nashik, Maharashtra 422005, India</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>079722 32147</t>
+          <t>097305 74449</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>848</v>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>No website</t>
+        <v>64</v>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Social media only</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Strong reviews, no way to showcase/book online</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr"/>
+          <t>Good social presence, missing a proper website</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/its_purohitscafe?igsh=ZHNtY2p5amRtbjY3&amp;utm_source=qr</t>
+        </is>
+      </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>cafes in Pune</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>6 story | Qahani</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Sr. No - 13, A/1/2/3, Mullick Nagar, Wadgaon Sheri, Pune, Maharashtra 411014, India</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>092846 85990</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>693</v>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>No website</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Strong reviews, no way to showcase/book online</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>cafes in Nashik</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>The Breakfast Story Cafe &amp; Bistro</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Girikale Complex, College Rd, opp. KFC, Thatte Nagar, Nashik, Maharashtra 422005, India</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>097673 63709</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>509</v>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>No website</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Strong reviews, no way to showcase/book online</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>cafes in Pune</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Matcha Brew &amp; Bake</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Survey No.21, A/10, B Plot, S Main Rd, Ashok Chakra Society, Meera Nagar, Koregaon Park, Pune, Maharashtra 411001, India</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>099993 09921</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>214</v>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>No website</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Strong reviews, no way to showcase/book online</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K16"/>
+  <autoFilter ref="A1:L13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>